--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/Table1_OP_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/Table1_OP_Raw.xlsx
@@ -853,7 +853,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Endocrinology and Diabetes</t>
+          <t>Endocrinology and Diabetes</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
